--- a/大台架材料/VCU相关/VCU接口梳理 - 20260602.xlsx
+++ b/大台架材料/VCU相关/VCU接口梳理 - 20260602.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="9600" windowHeight="12280"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="VCU低压电路图" sheetId="1" r:id="rId1"/>
@@ -327,16 +327,16 @@
     <t>风扇1，高端</t>
   </si>
   <si>
-    <t>PWM HSO08</t>
-  </si>
-  <si>
-    <t>电机系统冷却</t>
+    <t>PWM LSO17</t>
+  </si>
+  <si>
+    <t>电机系统冷却,改为</t>
   </si>
   <si>
     <t>风扇2，高端</t>
   </si>
   <si>
-    <t>PWM HSO14</t>
+    <t>PWM LSO18</t>
   </si>
   <si>
     <t>电池系统冷却</t>
@@ -445,7 +445,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,19 +457,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -498,20 +485,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -661,7 +634,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -670,6 +643,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC00000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -706,12 +685,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -832,12 +805,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -856,12 +823,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -875,12 +836,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1071,200 +1026,194 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1278,68 +1227,68 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2055,10 +2004,10 @@
       <c r="C24" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="30"/>
+      <c r="E24" s="29"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:11">
       <c r="A25" s="27">
@@ -2070,10 +2019,10 @@
       <c r="C25" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="30"/>
+      <c r="E25" s="29"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="17">
@@ -2088,7 +2037,7 @@
       <c r="D26" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="31"/>
+      <c r="E26" s="25"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="17">
@@ -2118,7 +2067,7 @@
       <c r="D28" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="30" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2135,7 +2084,7 @@
       <c r="D29" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="30" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2152,7 +2101,7 @@
       <c r="D30" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="30" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2169,7 +2118,7 @@
       <c r="D31" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="30" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2180,213 +2129,213 @@
       <c r="B32" s="17">
         <v>25</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="26" t="s">
         <v>60</v>
       </c>
       <c r="D32" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="34"/>
+      <c r="F32" s="31"/>
       <c r="K32" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="33" s="4" customFormat="1" spans="1:11">
-      <c r="A33" s="35">
+      <c r="A33" s="32">
         <v>68</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="32">
         <v>56</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="D33" s="35" t="s">
+      <c r="D33" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="37" t="s">
+      <c r="E33" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F33" s="38" t="s">
+      <c r="F33" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="G33" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="I33" s="38" t="s">
+      <c r="I33" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="J33" s="38" t="s">
+      <c r="J33" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="K33" s="39" t="s">
+      <c r="K33" s="36" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="34" s="4" customFormat="1" spans="1:11">
-      <c r="A34" s="35">
+      <c r="A34" s="32">
         <v>49</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="32">
         <v>55</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="35"/>
-      <c r="E34" s="37" t="s">
+      <c r="D34" s="32"/>
+      <c r="E34" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="F34" s="38" t="s">
+      <c r="F34" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="G34" s="38" t="s">
+      <c r="G34" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H34" s="38" t="s">
+      <c r="H34" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="I34" s="38" t="s">
+      <c r="I34" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="J34" s="38" t="s">
+      <c r="J34" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="K34" s="39" t="s">
+      <c r="K34" s="36" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" s="4" customFormat="1" spans="1:11">
-      <c r="A35" s="35">
+      <c r="A35" s="32">
         <v>64</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="32">
         <v>57</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="E35" s="37" t="s">
+      <c r="E35" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="F35" s="38" t="s">
+      <c r="F35" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="39" t="s">
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="36" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" spans="1:11">
-      <c r="A36" s="35">
+      <c r="A36" s="32">
         <v>45</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="32">
         <v>76</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="35"/>
-      <c r="E36" s="37" t="s">
+      <c r="D36" s="32"/>
+      <c r="E36" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="F36" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="39" t="s">
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="36" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="37" s="4" customFormat="1" spans="1:11">
-      <c r="A37" s="35">
+      <c r="A37" s="32">
         <v>69</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="32">
         <v>54</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="39"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="36"/>
     </row>
     <row r="38" s="4" customFormat="1" spans="1:11">
-      <c r="A38" s="35">
+      <c r="A38" s="32">
         <v>50</v>
       </c>
-      <c r="B38" s="35">
+      <c r="B38" s="32">
         <v>73</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C38" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="35"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="39"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="36"/>
     </row>
     <row r="39" s="5" customFormat="1" spans="1:11">
-      <c r="A39" s="40">
+      <c r="A39" s="37">
         <v>89</v>
       </c>
-      <c r="B39" s="40">
+      <c r="B39" s="37">
         <v>86</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C39" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="D39" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="E39" s="28"/>
-      <c r="F39" s="41" t="s">
+      <c r="E39" s="38"/>
+      <c r="F39" s="39" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="40" s="5" customFormat="1" spans="1:11">
-      <c r="A40" s="40">
+      <c r="A40" s="37">
         <v>97</v>
       </c>
-      <c r="B40" s="40">
+      <c r="B40" s="37">
         <v>85</v>
       </c>
-      <c r="C40" s="28" t="s">
+      <c r="C40" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="D40" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="E40" s="28"/>
-      <c r="F40" s="41" t="s">
+      <c r="E40" s="38"/>
+      <c r="F40" s="39" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2397,13 +2346,13 @@
       <c r="B41" s="21">
         <v>95</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="42" t="s">
+      <c r="D41" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="43"/>
+      <c r="E41" s="41"/>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="21">
@@ -2412,13 +2361,13 @@
       <c r="B42" s="21">
         <v>96</v>
       </c>
-      <c r="C42" s="44" t="s">
+      <c r="C42" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="D42" s="42" t="s">
+      <c r="D42" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="43"/>
+      <c r="E42" s="41"/>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="21">
@@ -2427,13 +2376,13 @@
       <c r="B43" s="21">
         <v>110</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="42" t="s">
+      <c r="D43" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="43"/>
+      <c r="E43" s="41"/>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="21">
@@ -2442,13 +2391,13 @@
       <c r="B44" s="21">
         <v>89</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="D44" s="42" t="s">
+      <c r="D44" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="43"/>
+      <c r="E44" s="41"/>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="21">
@@ -2457,13 +2406,13 @@
       <c r="B45" s="21">
         <v>111</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="42" t="s">
+      <c r="D45" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="E45" s="43"/>
+      <c r="E45" s="41"/>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="21">
@@ -2472,13 +2421,13 @@
       <c r="B46" s="21">
         <v>103</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="42" t="s">
+      <c r="D46" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="43"/>
+      <c r="E46" s="41"/>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="21">
@@ -2487,13 +2436,13 @@
       <c r="B47" s="21">
         <v>88</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="42" t="s">
+      <c r="D47" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="43"/>
+      <c r="E47" s="41"/>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="21">
@@ -2502,13 +2451,13 @@
       <c r="B48" s="21">
         <v>109</v>
       </c>
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="42" t="s">
+      <c r="D48" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="43"/>
+      <c r="E48" s="41"/>
     </row>
     <row r="49" ht="13.15" customHeight="1" spans="1:5">
       <c r="A49" s="21">
@@ -2517,13 +2466,13 @@
       <c r="B49" s="21">
         <v>101</v>
       </c>
-      <c r="C49" s="44" t="s">
+      <c r="C49" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="42" t="s">
+      <c r="D49" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="43" t="s">
+      <c r="E49" s="41" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2534,13 +2483,13 @@
       <c r="B50" s="21">
         <v>106</v>
       </c>
-      <c r="C50" s="42" t="s">
+      <c r="C50" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="D50" s="42" t="s">
+      <c r="D50" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="E50" s="43"/>
+      <c r="E50" s="41"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="21">
@@ -2549,13 +2498,13 @@
       <c r="B51" s="21">
         <v>94</v>
       </c>
-      <c r="C51" s="42" t="s">
+      <c r="C51" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="D51" s="42" t="s">
+      <c r="D51" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="43"/>
+      <c r="E51" s="41"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="21">
@@ -2564,26 +2513,26 @@
       <c r="B52" s="21">
         <v>114</v>
       </c>
-      <c r="C52" s="42" t="s">
+      <c r="C52" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="D52" s="42" t="s">
+      <c r="D52" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="E52" s="43"/>
+      <c r="E52" s="41"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="13"/>
       <c r="B53" s="13">
         <v>72</v>
       </c>
-      <c r="C53" s="45" t="s">
+      <c r="C53" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="45" t="s">
+      <c r="D53" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="E53" s="46" t="s">
+      <c r="E53" s="44" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2594,13 +2543,13 @@
       <c r="B54" s="13">
         <v>98</v>
       </c>
-      <c r="C54" s="45" t="s">
+      <c r="C54" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="E54" s="46" t="s">
+      <c r="E54" s="44" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2611,11 +2560,11 @@
       <c r="B55" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="45" t="s">
+      <c r="C55" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="D55" s="45"/>
-      <c r="E55" s="46" t="s">
+      <c r="D55" s="43"/>
+      <c r="E55" s="44" t="s">
         <v>128</v>
       </c>
     </row>
